--- a/Webccam_checkQr/Sổ làm việc1.xlsx
+++ b/Webccam_checkQr/Sổ làm việc1.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Study &amp; Work in University\University\tài liệu học phần\Thực tập\Webccam_checkQr\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380B2142-14D6-4FAE-AABE-5B750749E18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{432F6663-31DF-478F-A2B0-C3898D14FD4C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Trang_tính1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,16 +56,16 @@
     <t>SPXVN04133177633A</t>
   </si>
   <si>
-    <t>Thanh Xuân , ngõ 32, ngách 4, Hà Nội</t>
-  </si>
-  <si>
     <t>SPXVN04133177633B</t>
+  </si>
+  <si>
+    <t>Thanh Xuân, ngõ 32, ngách 4, Hà Nội</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -106,7 +100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -122,11 +116,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0752FF2-364A-4D53-B39A-A60119E74077}" name="Table1" displayName="Table1" ref="A1:B5" totalsRowShown="0">
-  <autoFilter ref="A1:B5" xr:uid="{D0752FF2-364A-4D53-B39A-A60119E74077}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B5" totalsRowShown="0">
+  <autoFilter ref="A1:B5"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D878F438-6277-4808-9D43-E3CFD1A66B7B}" name="QR"/>
-    <tableColumn id="2" xr3:uid="{84663678-EC04-4064-9E32-457C160A1557}" name="Address"/>
+    <tableColumn id="1" name="QR"/>
+    <tableColumn id="2" name="Address"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -175,7 +169,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -227,7 +221,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -421,14 +415,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8E09972-372E-4D4F-AA83-E48554B9DDC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -470,10 +464,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
